--- a/results/human_health_breakdown/2050/propanol production, biogas, fossil ethylene.xlsx
+++ b/results/human_health_breakdown/2050/propanol production, biogas, fossil ethylene.xlsx
@@ -444,7 +444,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2.409259660677909E-06</v>
+        <v>2.376395186557615E-06</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -478,7 +478,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>1.256570503462829E-08</v>
+        <v>1.25657050346283E-08</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -495,7 +495,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>1.91370641990796E-07</v>
+        <v>1.913706419907961E-07</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -512,7 +512,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>1.323009719672109E-06</v>
+        <v>1.323009719672113E-06</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -529,7 +529,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>3.486878314800316E-08</v>
+        <v>2.220231505145643E-09</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -546,7 +546,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>1.136059244902401E-10</v>
+        <v>3.263180440601349E-12</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -563,7 +563,7 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>1.099006421235103E-10</v>
+        <v>4.319809927078553E-12</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -580,7 +580,7 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>2.84590817277904E-08</v>
+        <v>2.845908172779045E-08</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -614,7 +614,7 @@
         <v>14</v>
       </c>
       <c r="D12">
-        <v>3.125438660186343E-07</v>
+        <v>3.125438660186344E-07</v>
       </c>
       <c r="E12">
         <v>1</v>
